--- a/src/data/graph/case_study/sector_5_insight/s002_insights.xlsx
+++ b/src/data/graph/case_study/sector_5_insight/s002_insights.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="11060" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="11120" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="s002_insights" sheetId="1" r:id="rId1"/>
@@ -1517,7 +1517,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="134.2" spans="1:7">
+    <row r="3" ht="409.5" spans="1:7">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" ht="409.5" spans="1:7">
       <c r="A10" t="s">
         <v>49</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" ht="302.2" spans="1:7">
+    <row r="12" ht="409.5" spans="1:7">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -1749,7 +1749,7 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G12" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:G12">
+    <sortState ref="A1:G12">
       <sortCondition ref="D1" descending="1"/>
     </sortState>
     <extLst/>
@@ -1768,7 +1768,7 @@
     <col min="1" max="1" width="13.4140625" customWidth="1"/>
     <col min="2" max="2" width="48.4375" customWidth="1"/>
     <col min="3" max="3" width="34.8984375" customWidth="1"/>
-    <col min="4" max="4" width="17.9609375" customWidth="1"/>
+    <col min="4" max="4" width="46.34375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" spans="1:4">
